--- a/diseases/d064/2015-2019.xlsx
+++ b/diseases/d064/2015-2019.xlsx
@@ -1157,6 +1157,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1683,6 +1688,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2403,6 +2413,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2544,6 +2559,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3264,6 +3284,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3405,6 +3430,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4125,6 +4155,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4266,6 +4301,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4986,6 +5026,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5271,6 +5316,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5991,6 +6041,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6132,6 +6187,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6852,6 +6912,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6993,6 +7058,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7857,6 +7927,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7998,6 +8073,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8718,6 +8798,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8859,6 +8944,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9579,6 +9669,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9720,6 +9815,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO63" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10584,6 +10684,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO69" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10725,6 +10830,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO70" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11445,6 +11555,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO75" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11586,6 +11701,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO76" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12691,6 +12811,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO83" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13361,6 +13486,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO87" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14081,6 +14211,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO92" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14222,6 +14357,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO93" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14942,6 +15082,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO98" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15083,6 +15228,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO99" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15803,6 +15953,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO104" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16088,6 +16243,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO106" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16808,6 +16968,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO111" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16949,6 +17114,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO112" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17669,6 +17839,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO117" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17810,6 +17985,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO118" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18530,6 +18710,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO123" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18815,6 +19000,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO125" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19535,6 +19725,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO130" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19676,6 +19871,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO131" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20396,6 +20596,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO136" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20537,6 +20742,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO137" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21401,6 +21611,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO143" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21542,6 +21757,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO144" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22262,6 +22482,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO149" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22403,6 +22628,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO150" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23123,6 +23353,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO155" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23264,6 +23499,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO156" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24513,6 +24753,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO164" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25039,6 +25284,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO167" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25759,6 +26009,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO172" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25900,6 +26155,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO173" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26620,6 +26880,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO178" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26761,6 +27026,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO179" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27625,6 +27895,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO185" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27766,6 +28041,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO186" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28486,6 +28766,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA191" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO191" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28627,6 +28912,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO192" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29347,6 +29637,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA197" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO197" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29488,6 +29783,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO198" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30352,6 +30652,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO204" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30493,6 +30798,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA205" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO205" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31213,6 +31523,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO210" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31354,6 +31669,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA211" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO211" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32074,6 +32394,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA216" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO216" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32359,6 +32684,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA218" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO218" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33079,6 +33409,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA223" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO223" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33220,6 +33555,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA224" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO224" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33940,6 +34280,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA229" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO229" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34081,6 +34426,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA230" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO230" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34801,6 +35151,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA235" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO235" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35086,6 +35441,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA237" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO237" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36191,6 +36551,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA244" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO244" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36717,6 +37082,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA247" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO247" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37437,6 +37807,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA252" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO252" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37578,6 +37953,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA253" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO253" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38298,6 +38678,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA258" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO258" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38439,6 +38824,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA259" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO259" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39303,6 +39693,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA265" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO265" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39444,6 +39839,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA266" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO266" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40164,6 +40564,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA271" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO271" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40305,6 +40710,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA272" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO272" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41025,6 +41435,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA277" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO277" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41310,6 +41725,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA279" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO279" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42030,6 +42450,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA284" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO284" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42171,6 +42596,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA285" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO285" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42891,6 +43321,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA290" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO290" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43032,6 +43467,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA291" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO291" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43896,6 +44336,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA297" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO297" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44037,6 +44482,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA298" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO298" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44757,6 +45207,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA303" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO303" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44898,6 +45353,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA304" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO304" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45618,6 +46078,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA309" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO309" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45759,6 +46224,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA310" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO310" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46623,6 +47093,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA316" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO316" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46764,6 +47239,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA317" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO317" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -47869,6 +48349,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA324" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO324" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48395,6 +48880,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA327" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO327" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49115,6 +49605,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA332" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO332" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49400,6 +49895,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA334" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO334" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49976,6 +50476,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA338" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO338" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50261,6 +50766,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA340" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO340" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50981,6 +51491,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA345" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO345" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51122,6 +51637,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA346" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO346" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51842,6 +52362,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA351" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO351" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51983,6 +52508,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA352" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO352" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52847,6 +53377,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA358" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO358" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52988,6 +53523,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA359" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO359" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -53708,6 +54248,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA364" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO364" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -53849,6 +54394,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA365" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO365" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54569,6 +55119,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA370" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO370" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54710,6 +55265,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA371" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO371" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -55574,6 +56134,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA377" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO377" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -55715,6 +56280,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA378" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO378" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -56435,6 +57005,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA383" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO383" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -56576,6 +57151,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA384" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO384" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -57296,6 +57876,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA389" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO389" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -57581,6 +58166,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA391" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO391" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -58301,6 +58891,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA396" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO396" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -58440,6 +59035,11 @@
       <c r="S397" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA397" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO397" t="inlineStr">
